--- a/exports/ALKEM_full_report.xlsx
+++ b/exports/ALKEM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.23</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44578.55208333334</v>
+        <v>44579.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>3583.9</v>
+        <v>3540</v>
       </c>
       <c r="I2" t="n">
         <v>3569.321305</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.39</v>
+        <v>-5.56</v>
       </c>
       <c r="L2" t="n">
-        <v>4.75</v>
+        <v>5.82</v>
       </c>
       <c r="M2" t="n">
         <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>2.11</v>
+        <v>2.48</v>
       </c>
       <c r="O2" t="n">
         <v>1.52</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.05</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44631.55208333334</v>
+        <v>44634.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>3389.8</v>
+        <v>3400.3</v>
       </c>
       <c r="I3" t="n">
         <v>3392.855211621084</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K3" t="n">
-        <v>4.24</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
         <v>1.96</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.33</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44662.55208333334</v>
+        <v>44663.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>3472</v>
+        <v>3453</v>
       </c>
       <c r="I4" t="n">
         <v>3470.806536873457</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K4" t="n">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="L4" t="n">
         <v>1.48</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.72</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44711.55208333334</v>
+        <v>44712.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>3082</v>
+        <v>3136.8</v>
       </c>
       <c r="I5" t="n">
         <v>3111.388917374125</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K5" t="n">
-        <v>10.74</v>
+        <v>9.16</v>
       </c>
       <c r="L5" t="n">
         <v>1.8</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>6.74</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44733.55208333334</v>
+        <v>44734.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>3084</v>
+        <v>3012.6</v>
       </c>
       <c r="I6" t="n">
         <v>3017.215035306734</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.68</v>
+        <v>-3.96</v>
       </c>
       <c r="L6" t="n">
-        <v>3.6</v>
+        <v>4.46</v>
       </c>
       <c r="M6" t="n">
         <v>2.04</v>
       </c>
       <c r="N6" t="n">
-        <v>2.05</v>
+        <v>3.11</v>
       </c>
       <c r="O6" t="n">
         <v>2.53</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>7.04</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44750.55208333334</v>
+        <v>44753.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>3117</v>
+        <v>3178.8</v>
       </c>
       <c r="I7" t="n">
         <v>3126.117398524978</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.47</v>
+        <v>-5.52</v>
       </c>
       <c r="L7" t="n">
-        <v>5.56</v>
+        <v>5.89</v>
       </c>
       <c r="M7" t="n">
         <v>0.86</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>5.6</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44764.55208333334</v>
+        <v>44767.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>3165.5</v>
+        <v>3123.5</v>
       </c>
       <c r="I8" t="n">
         <v>3128.831770702986</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.42</v>
+        <v>-1.74</v>
       </c>
       <c r="L8" t="n">
         <v>3.35</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>5.84</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44770.55208333334</v>
+        <v>44771.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>3223</v>
+        <v>3236.65</v>
       </c>
       <c r="I9" t="n">
         <v>3225.109360764949</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.19</v>
+        <v>-3.62</v>
       </c>
       <c r="L9" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="M9" t="n">
         <v>0.32</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>5.68</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44775.55208333334</v>
+        <v>44776.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>3190</v>
+        <v>3055.45</v>
       </c>
       <c r="I10" t="n">
         <v>3071.157917680715</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.44</v>
+        <v>-5.6</v>
       </c>
       <c r="L10" t="n">
-        <v>2.06</v>
+        <v>5.76</v>
       </c>
       <c r="M10" t="n">
-        <v>-0</v>
+        <v>0.31</v>
       </c>
       <c r="N10" t="n">
-        <v>0.78</v>
+        <v>2.35</v>
       </c>
       <c r="O10" t="n">
         <v>0.06</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.76</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44805.55208333334</v>
+        <v>44806.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>2956</v>
+        <v>3000</v>
       </c>
       <c r="I11" t="n">
         <v>2993.564991244372</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>1.81</v>
       </c>
       <c r="L11" t="n">
         <v>5.55</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>4.11</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44841.55208333334</v>
+        <v>44844.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>3200</v>
+        <v>3159</v>
       </c>
       <c r="I12" t="n">
         <v>3159.03175427505</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K12" t="n">
-        <v>6.67</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.6</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>5.53</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44865.55208333334</v>
+        <v>44866.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>3155.5</v>
+        <v>3231.45</v>
       </c>
       <c r="I13" t="n">
         <v>3220.201454487183</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K13" t="n">
-        <v>0.11</v>
+        <v>-2.29</v>
       </c>
       <c r="L13" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>1.46</v>
+        <v>1.98</v>
       </c>
       <c r="O13" t="n">
         <v>-0.95</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.39</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44874.38541666666</v>
+        <v>44874.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>3199.9</v>
+        <v>3174.05</v>
       </c>
       <c r="I14" t="n">
         <v>3176.272210729944</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.98</v>
+        <v>-1.78</v>
       </c>
       <c r="L14" t="n">
         <v>2.77</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>4.58</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44964.55208333334</v>
+        <v>44965.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>3053</v>
+        <v>3150.5</v>
       </c>
       <c r="I15" t="n">
         <v>3102.741260219716</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>90</v>
+        <v>90.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>3.81</v>
+        <v>0.74</v>
       </c>
       <c r="L15" t="n">
         <v>1.6</v>
@@ -1296,7 +1475,7 @@
         <v>1.38</v>
       </c>
       <c r="N15" t="n">
-        <v>1.97</v>
+        <v>4.25</v>
       </c>
       <c r="O15" t="n">
         <v>-1.51</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.61</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44986.38541666666</v>
+        <v>44986.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>3167</v>
+        <v>3119.9</v>
       </c>
       <c r="I16" t="n">
         <v>3160.281134958746</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>0.52</v>
+        <v>-0.97</v>
       </c>
       <c r="L16" t="n">
         <v>3.14</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>5.75</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45009.55208333334</v>
+        <v>45012.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>3169.7</v>
+        <v>3238.15</v>
       </c>
       <c r="I17" t="n">
         <v>3197.760370352248</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.6</v>
+        <v>-3.79</v>
       </c>
       <c r="L17" t="n">
-        <v>3.37</v>
+        <v>4.65</v>
       </c>
       <c r="M17" t="n">
         <v>1.76</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.82</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45057.55208333334</v>
+        <v>45058.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>3499.95</v>
+        <v>3451.1</v>
       </c>
       <c r="I18" t="n">
         <v>3480.035308588832</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K18" t="n">
-        <v>8.08</v>
+        <v>6.58</v>
       </c>
       <c r="L18" t="n">
         <v>2.48</v>
@@ -1467,7 +1682,7 @@
         <v>0.61</v>
       </c>
       <c r="N18" t="n">
-        <v>2.16</v>
+        <v>2.59</v>
       </c>
       <c r="O18" t="n">
         <v>1.59</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>4.81</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45084.38541666666</v>
+        <v>45084.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>3400.5</v>
+        <v>3415</v>
       </c>
       <c r="I19" t="n">
         <v>3406.991386660168</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>1.47</v>
+        <v>1.05</v>
       </c>
       <c r="L19" t="n">
         <v>1.64</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>3.96</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45148.55208333334</v>
+        <v>45149.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>4140</v>
+        <v>3850</v>
       </c>
       <c r="I20" t="n">
         <v>4011.75705622676</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>64</v>
+        <v>64.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>21.23</v>
+        <v>12.74</v>
       </c>
       <c r="L20" t="n">
         <v>3.16</v>
       </c>
       <c r="M20" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="N20" t="n">
-        <v>2.13</v>
+        <v>7.87</v>
       </c>
       <c r="O20" t="n">
         <v>0.74</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10.24</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45182.38541666666</v>
+        <v>45182.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>3716.65</v>
+        <v>3748.7</v>
       </c>
       <c r="I21" t="n">
         <v>3747.966431957167</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K21" t="n">
-        <v>3.46</v>
+        <v>2.63</v>
       </c>
       <c r="L21" t="n">
         <v>6.51</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>4.39</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45190.55208333334</v>
+        <v>45191.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>3650</v>
+        <v>3564.4</v>
       </c>
       <c r="I22" t="n">
         <v>3587.049493188126</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.63</v>
+        <v>-4.92</v>
       </c>
       <c r="L22" t="n">
-        <v>3.51</v>
+        <v>5.54</v>
       </c>
       <c r="M22" t="n">
         <v>0.67</v>
       </c>
       <c r="N22" t="n">
-        <v>1.21</v>
+        <v>2.68</v>
       </c>
       <c r="O22" t="n">
         <v>3.1</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.56</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45216.55208333334</v>
+        <v>45217.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>3620.9</v>
+        <v>3623.95</v>
       </c>
       <c r="I23" t="n">
         <v>3623.39243148276</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.59</v>
+        <v>-1.67</v>
       </c>
       <c r="L23" t="n">
         <v>2.74</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>3.28</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45302.38541666666</v>
+        <v>45302.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>5070.75</v>
+        <v>5044.2</v>
       </c>
       <c r="I24" t="n">
         <v>5052.160373218452</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>85</v>
+        <v>85.16666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>39.92</v>
+        <v>39.19</v>
       </c>
       <c r="L24" t="n">
         <v>3.15</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>4.77</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45328.38541666666</v>
+        <v>45328.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>4980</v>
+        <v>5065.05</v>
       </c>
       <c r="I25" t="n">
         <v>5062.97169120828</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K25" t="n">
-        <v>1.27</v>
+        <v>-0.41</v>
       </c>
       <c r="L25" t="n">
         <v>3.68</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>6.97</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45345.55208333334</v>
+        <v>45348.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>5382</v>
+        <v>4771.4</v>
       </c>
       <c r="I26" t="n">
         <v>5145.92430235846</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>6.26</v>
+        <v>-5.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.93</v>
+        <v>8.02</v>
       </c>
       <c r="M26" t="n">
         <v>0.41</v>
       </c>
       <c r="N26" t="n">
-        <v>3.55</v>
+        <v>6.82</v>
       </c>
       <c r="O26" t="n">
         <v>3.04</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>16.09</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45377.55208333334</v>
+        <v>45378.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>5002.25</v>
+        <v>5040</v>
       </c>
       <c r="I27" t="n">
         <v>5037.295083513661</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.84</v>
+        <v>-5.63</v>
       </c>
       <c r="L27" t="n">
         <v>13.46</v>
       </c>
       <c r="M27" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>4.54</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.59</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45397.38541666666</v>
+        <v>45397.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>4732</v>
+        <v>4702.2</v>
       </c>
       <c r="I28" t="n">
         <v>4721.959500706687</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.11</v>
+        <v>-6.7</v>
       </c>
       <c r="L28" t="n">
         <v>7.29</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>5.06</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45407.38541666666</v>
+        <v>45407.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>4805.95</v>
+        <v>4860</v>
       </c>
       <c r="I29" t="n">
         <v>4834.078758947049</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.21</v>
+        <v>-3.36</v>
       </c>
       <c r="L29" t="n">
-        <v>2.36</v>
+        <v>3.76</v>
       </c>
       <c r="M29" t="n">
         <v>0.62</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>5.41</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>5280</v>
+        <v>4951.45</v>
       </c>
       <c r="I30" t="n">
         <v>5134.22973234233</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K30" t="n">
-        <v>8.640000000000001</v>
+        <v>1.88</v>
       </c>
       <c r="L30" t="n">
         <v>2.48</v>
       </c>
       <c r="M30" t="n">
-        <v>0.44</v>
+        <v>3.03</v>
       </c>
       <c r="N30" t="n">
-        <v>2.23</v>
+        <v>6.02</v>
       </c>
       <c r="O30" t="n">
         <v>3.11</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.02</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45455.38541666666</v>
+        <v>45455.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>5070.8</v>
+        <v>5090</v>
       </c>
       <c r="I31" t="n">
         <v>5085.843055231673</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.41</v>
+        <v>-2.8</v>
       </c>
       <c r="L31" t="n">
         <v>4.01</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.82</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45552.55208333334</v>
+        <v>45553.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>6236.4</v>
+        <v>6093.4</v>
       </c>
       <c r="I32" t="n">
         <v>6121.246982153269</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>97</v>
+        <v>97.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>22.52</v>
+        <v>19.71</v>
       </c>
       <c r="L32" t="n">
         <v>4.28</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>6.02</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>6182.85</v>
+        <v>6296.9</v>
       </c>
       <c r="I33" t="n">
         <v>6273.606588767836</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.47</v>
+        <v>-3.34</v>
       </c>
       <c r="L33" t="n">
-        <v>2.8</v>
+        <v>3.66</v>
       </c>
       <c r="M33" t="n">
         <v>1.05</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>6.89</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45588.38541666666</v>
+        <v>45588.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>6033.95</v>
+        <v>5858</v>
       </c>
       <c r="I34" t="n">
         <v>5983.781924371969</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.18</v>
+        <v>-6.97</v>
       </c>
       <c r="L34" t="n">
-        <v>4.75</v>
+        <v>7.81</v>
       </c>
       <c r="M34" t="n">
         <v>0.13</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.53</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45656.55208333334</v>
+        <v>45657.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>5522.6</v>
+        <v>5655.6</v>
       </c>
       <c r="I35" t="n">
         <v>5597.299659710324</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>68</v>
+        <v>68.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>5.73</v>
+        <v>3.46</v>
       </c>
       <c r="L35" t="n">
         <v>3.87</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>5.42</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>5420.6</v>
+        <v>5377.45</v>
       </c>
       <c r="I36" t="n">
         <v>5385.039745087111</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.16</v>
+        <v>-4.92</v>
       </c>
       <c r="L36" t="n">
-        <v>4.17</v>
+        <v>5.03</v>
       </c>
       <c r="M36" t="n">
         <v>0.43</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.74</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45693.55208333334</v>
+        <v>45694.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>5100.8</v>
+        <v>5224.75</v>
       </c>
       <c r="I37" t="n">
         <v>5188.031984355405</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K37" t="n">
-        <v>5.14</v>
+        <v>2.84</v>
       </c>
       <c r="L37" t="n">
         <v>1.75</v>
@@ -2550,7 +2993,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>2.18</v>
+        <v>3.22</v>
       </c>
       <c r="O37" t="n">
         <v>-1.63</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>6.23</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45695.55208333334</v>
+        <v>45698.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>5152.3</v>
+        <v>4825</v>
       </c>
       <c r="I38" t="n">
         <v>4990.761165960643</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.39</v>
+        <v>-7.65</v>
       </c>
       <c r="L38" t="n">
-        <v>3.61</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>0.11</v>
+        <v>1.11</v>
       </c>
       <c r="N38" t="n">
-        <v>2.14</v>
+        <v>6.84</v>
       </c>
       <c r="O38" t="n">
         <v>3.22</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.86</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45733.38541666666</v>
+        <v>45733.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>4784</v>
+        <v>4840</v>
       </c>
       <c r="I39" t="n">
         <v>4803.259268813506</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K39" t="n">
-        <v>0.85</v>
+        <v>-0.31</v>
       </c>
       <c r="L39" t="n">
         <v>5.6</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.99</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45744.55208333334</v>
+        <v>45748.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>4866.8</v>
+        <v>4830</v>
       </c>
       <c r="I40" t="n">
         <v>4833.267689018507</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>11</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>0.55</v>
+        <v>-0.21</v>
       </c>
       <c r="L40" t="n">
         <v>1.36</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.73</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45768.38541666666</v>
+        <v>45768.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>4967</v>
+        <v>5003.9</v>
       </c>
       <c r="I41" t="n">
         <v>5002.320769094106</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.84</v>
+        <v>-3.6</v>
       </c>
       <c r="L41" t="n">
         <v>3.79</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>4.65</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>4981</v>
+        <v>4924.5</v>
       </c>
       <c r="I42" t="n">
         <v>4980.013015969601</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.46</v>
+        <v>-1.59</v>
       </c>
       <c r="L42" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="M42" t="n">
         <v>1.19</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>5.03</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45790.38541666666</v>
+        <v>45790.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>5087</v>
+        <v>5145</v>
       </c>
       <c r="I43" t="n">
         <v>5108.803655590456</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.3</v>
+        <v>-4.48</v>
       </c>
       <c r="L43" t="n">
-        <v>4.07</v>
+        <v>4.48</v>
       </c>
       <c r="M43" t="n">
         <v>0.49</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>5.36</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45807.55208333334</v>
+        <v>45810.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>5102.5</v>
+        <v>5051</v>
       </c>
       <c r="I44" t="n">
         <v>5062.572331218769</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.83</v>
+        <v>-1.83</v>
       </c>
       <c r="L44" t="n">
-        <v>1.97</v>
+        <v>2.74</v>
       </c>
       <c r="M44" t="n">
         <v>4.04</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>6.05</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45852.55208333334</v>
+        <v>45853.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>4856.3</v>
+        <v>4913.7</v>
       </c>
       <c r="I45" t="n">
         <v>4874.744488353548</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K45" t="n">
-        <v>3.85</v>
+        <v>2.72</v>
       </c>
       <c r="L45" t="n">
         <v>1.33</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>4.28</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45869.55208333334</v>
+        <v>45870.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>5015</v>
+        <v>4902</v>
       </c>
       <c r="I46" t="n">
         <v>4936.265088783995</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K46" t="n">
-        <v>2.06</v>
+        <v>-0.24</v>
       </c>
       <c r="L46" t="n">
         <v>1.58</v>
@@ -3063,7 +3614,7 @@
         <v>0.25</v>
       </c>
       <c r="N46" t="n">
-        <v>1.78</v>
+        <v>3.33</v>
       </c>
       <c r="O46" t="n">
         <v>1.44</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>4.94</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45881.38541666666</v>
+        <v>45881.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>4980</v>
+        <v>5165</v>
       </c>
       <c r="I47" t="n">
         <v>5005.331021608833</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.59</v>
+        <v>-5.37</v>
       </c>
       <c r="L47" t="n">
-        <v>2.73</v>
+        <v>6.23</v>
       </c>
       <c r="M47" t="n">
         <v>0.49</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.15</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45926.55208333334</v>
+        <v>45929.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>5413.5</v>
+        <v>5400</v>
       </c>
       <c r="I48" t="n">
         <v>5411.436652030833</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>45</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K48" t="n">
-        <v>4.81</v>
+        <v>4.55</v>
       </c>
       <c r="L48" t="n">
         <v>3.66</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>4.1</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45964.38541666666</v>
+        <v>45964.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>5557.5</v>
+        <v>5635</v>
       </c>
       <c r="I49" t="n">
         <v>5608.846583751047</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.92</v>
+        <v>-4.35</v>
       </c>
       <c r="L49" t="n">
         <v>4.59</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>4.43</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46001.38541666666</v>
+        <v>46001.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>5629.5</v>
+        <v>5582</v>
       </c>
       <c r="I50" t="n">
         <v>5582.883037250424</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>36.83333333333334</v>
+        <v>37</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.1</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L50" t="n">
         <v>1.51</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>4.16</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46027.55208333334</v>
+        <v>46028.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>5569.5</v>
+        <v>5640.5</v>
       </c>
       <c r="I51" t="n">
         <v>5638.186314454799</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>0.22</v>
+        <v>-1.05</v>
       </c>
       <c r="L51" t="n">
         <v>2.07</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>4.55</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46054.38541666666</v>
+        <v>46054.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>5610</v>
+        <v>5590</v>
       </c>
       <c r="I52" t="n">
         <v>5607.87625726853</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.54</v>
+        <v>-0.9</v>
       </c>
       <c r="L52" t="n">
         <v>2.38</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>5.25</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46063.55208333334</v>
+        <v>46064.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>5781</v>
+        <v>5882.5</v>
       </c>
       <c r="I53" t="n">
         <v>5819.500879447942</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.42</v>
+        <v>-5.23</v>
       </c>
       <c r="L53" t="n">
-        <v>4.35</v>
+        <v>5.81</v>
       </c>
       <c r="M53" t="n">
         <v>3.33</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>6.39</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46066.38541666666</v>
+        <v>46066.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>5735</v>
+        <v>5400</v>
       </c>
       <c r="I54" t="n">
         <v>5586.367629479196</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.51</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>2.62</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M54" t="n">
         <v>0.12</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>10.51</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46078.55208333334</v>
+        <v>46079.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>5646</v>
+        <v>5687.5</v>
       </c>
       <c r="I55" t="n">
         <v>5651.481007719515</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.56</v>
+        <v>-5.32</v>
       </c>
       <c r="L55" t="n">
         <v>7.21</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>4.65</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46092.55208333334</v>
+        <v>46093.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>5530</v>
+        <v>5439</v>
       </c>
       <c r="I56" t="n">
         <v>5459.220478453342</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.77</v>
+        <v>-4.37</v>
       </c>
       <c r="L56" t="n">
         <v>4.79</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>6.22</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>5301</v>
+        <v>5438.5</v>
       </c>
       <c r="I57" t="n">
         <v>5400.325120431735</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K57" t="n">
-        <v>2.54</v>
+        <v>0.01</v>
       </c>
       <c r="L57" t="n">
         <v>1.64</v>
       </c>
       <c r="M57" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="N57" t="n">
         <v>2.73</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.01</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46118.55208333334</v>
+        <v>46119.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>5231.5</v>
+        <v>5163.5</v>
       </c>
       <c r="I58" t="n">
         <v>5174.529113484738</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.81</v>
+        <v>-5.06</v>
       </c>
       <c r="L58" t="n">
         <v>6.68</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>6.76</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46125.55208333334</v>
+        <v>46127.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>5349</v>
+        <v>5562</v>
       </c>
       <c r="I59" t="n">
         <v>5459.782265105633</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.59</v>
+        <v>-7.72</v>
       </c>
       <c r="L59" t="n">
-        <v>5.58</v>
+        <v>7.78</v>
       </c>
       <c r="M59" t="n">
         <v>2.13</v>
       </c>
       <c r="N59" t="n">
-        <v>2.45</v>
+        <v>4.49</v>
       </c>
       <c r="O59" t="n">
         <v>-1.21</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>7.62</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46136.38541666666</v>
+        <v>46136.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>5455.5</v>
+        <v>5240</v>
       </c>
       <c r="I60" t="n">
         <v>5405.236574183773</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.91</v>
+        <v>-5.79</v>
       </c>
       <c r="L60" t="n">
-        <v>3.81</v>
+        <v>6.63</v>
       </c>
       <c r="M60" t="n">
         <v>0.3</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46203.38541666666</v>
+        <v>46203.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>5520.5</v>
+        <v>5599</v>
       </c>
       <c r="I61" t="n">
         <v>5536.390635314407</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>66.83333333333333</v>
+        <v>67</v>
       </c>
       <c r="K61" t="n">
-        <v>-5.35</v>
+        <v>-6.85</v>
       </c>
       <c r="L61" t="n">
         <v>10.48</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>4.73</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46240.55208333334</v>
+        <v>46241.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>5598.5</v>
+        <v>5595.5</v>
       </c>
       <c r="I62" t="n">
         <v>5597.595513869675</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>37</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="L62" t="n">
         <v>2</v>
       </c>
       <c r="M62" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="N62" t="n">
         <v>2.61</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>3.47</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46281.55208333334</v>
+        <v>46282.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>5180.5</v>
+        <v>5291.5</v>
       </c>
       <c r="I63" t="n">
         <v>5268.093704505141</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K63" t="n">
-        <v>7.42</v>
+        <v>5.43</v>
       </c>
       <c r="L63" t="n">
         <v>1.87</v>
@@ -4032,7 +4787,7 @@
         <v>1.58</v>
       </c>
       <c r="N63" t="n">
-        <v>2.33</v>
+        <v>2.89</v>
       </c>
       <c r="O63" t="n">
         <v>0.63</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>5.52</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46293.38541666666</v>
+        <v>46293.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>5243.5</v>
+        <v>5141</v>
       </c>
       <c r="I64" t="n">
         <v>5205.013984795502</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.91</v>
+        <v>-2.84</v>
       </c>
       <c r="L64" t="n">
-        <v>2.46</v>
+        <v>3.03</v>
       </c>
       <c r="M64" t="n">
         <v>0.76</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,14 @@
       <c r="Q65" t="n">
         <v>41</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6251,7 +7038,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.4</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="6">
@@ -6261,7 +7048,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="7">
@@ -6271,7 +7058,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="8">
@@ -6281,7 +7068,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -6291,7 +7078,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="10">
@@ -6301,7 +7088,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.4</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="11">
@@ -6341,7 +7128,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="15">
@@ -6351,7 +7138,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.57</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="16">
@@ -6361,7 +7148,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.19</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="17">
@@ -6371,7 +7158,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>39.92</v>
+        <v>39.19</v>
       </c>
     </row>
     <row r="18">
@@ -6381,7 +7168,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42.9</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="19">
@@ -6391,7 +7178,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.55</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="20">
@@ -6401,7 +7188,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.15</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="21">
@@ -6421,7 +7208,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -6441,7 +7228,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="25">
@@ -6461,7 +7248,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.73</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="27">
@@ -6471,7 +7258,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.8</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="28">
@@ -6481,7 +7268,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
